--- a/FPE/Literatura/FPE.xlsx
+++ b/FPE/Literatura/FPE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Downloads\FPE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/FPE/Literatura/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE88983-715A-4F9B-995C-67E3E2EFF0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7DE88983-715A-4F9B-995C-67E3E2EFF0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{124E309C-CCFA-4BE4-B651-4A7ED15A577E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{238679F9-9728-4825-AE47-38AF6487A4B3}"/>
   </bookViews>
@@ -221,9 +221,6 @@
     <t>Aporta un marco FPE para conservación y biodiversidad.</t>
   </si>
   <si>
-    <t>Resurrección et al.</t>
-  </si>
-  <si>
     <t>Examina cómo los proyectos de restauración reproducen exclusiones al ignorar relaciones históricas de poder y saberes locales.</t>
   </si>
   <si>
@@ -309,6 +306,9 @@
   </si>
   <si>
     <t>“Una ecología política feminista sitúa explícitamente el aire y los cuerpos que respiran, en su intra-acción corpomaterial, relacional y posthumana, en el centro del análisis.”</t>
+  </si>
+  <si>
+    <t>Elias et al.</t>
   </si>
 </sst>
 </file>
@@ -775,7 +775,7 @@
         <v>34</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -804,7 +804,7 @@
         <v>38</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>10</v>
@@ -833,7 +833,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
@@ -862,7 +862,7 @@
         <v>45</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>16</v>
@@ -874,7 +874,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -891,7 +891,7 @@
         <v>49</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>19</v>
@@ -920,7 +920,7 @@
         <v>52</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>53</v>
@@ -932,7 +932,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -949,7 +949,7 @@
         <v>57</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>58</v>
@@ -966,7 +966,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C9" s="1">
         <v>2021</v>
@@ -975,19 +975,19 @@
         <v>41</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -1001,22 +1001,22 @@
         <v>1995</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -1030,22 +1030,22 @@
         <v>2015</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -1062,19 +1062,19 @@
         <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
